--- a/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0001T0006Z000C1N6_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0001T0006Z000C1N6_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>15.97285721639016</v>
+        <v>2.595589297663401</v>
       </c>
       <c r="D2" t="n">
-        <v>19.62443205282801</v>
+        <v>3.188970208584552</v>
       </c>
       <c r="E2" t="n">
-        <v>11.6157786693359</v>
+        <v>1.887564033767084</v>
       </c>
       <c r="F2" t="n">
-        <v>11.45068155400384</v>
+        <v>1.860735752525624</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>11.86702898694821</v>
+        <v>1.928392210379084</v>
       </c>
       <c r="D3" t="n">
-        <v>13.55752172072982</v>
+        <v>2.203097279618596</v>
       </c>
       <c r="E3" t="n">
-        <v>11.6157786693359</v>
+        <v>1.887564033767084</v>
       </c>
       <c r="F3" t="n">
-        <v>11.45068155400384</v>
+        <v>1.860735752525624</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>31.65270494792034</v>
+        <v>5.143564554037056</v>
       </c>
       <c r="D4" t="n">
-        <v>31.01964313222367</v>
+        <v>5.040692008986346</v>
       </c>
       <c r="E4" t="n">
-        <v>11.6157786693359</v>
+        <v>1.887564033767084</v>
       </c>
       <c r="F4" t="n">
-        <v>11.45068155400384</v>
+        <v>1.860735752525624</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>34.66635632027617</v>
+        <v>5.633282902044878</v>
       </c>
       <c r="D5" t="n">
-        <v>34.35061829514843</v>
+        <v>5.58197547296162</v>
       </c>
       <c r="E5" t="n">
-        <v>11.6157786693359</v>
+        <v>1.887564033767084</v>
       </c>
       <c r="F5" t="n">
-        <v>11.45068155400384</v>
+        <v>1.860735752525624</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>29.23439104852088</v>
+        <v>4.750588545384643</v>
       </c>
       <c r="D6" t="n">
-        <v>28.60785124258492</v>
+        <v>4.64877582692005</v>
       </c>
       <c r="E6" t="n">
-        <v>11.6157786693359</v>
+        <v>1.887564033767084</v>
       </c>
       <c r="F6" t="n">
-        <v>11.45068155400384</v>
+        <v>1.860735752525624</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>27.98901844352041</v>
+        <v>4.548215497072066</v>
       </c>
       <c r="D7" t="n">
-        <v>27.80299020852914</v>
+        <v>4.517985908885986</v>
       </c>
       <c r="E7" t="n">
-        <v>11.6157786693359</v>
+        <v>1.887564033767084</v>
       </c>
       <c r="F7" t="n">
-        <v>11.45068155400384</v>
+        <v>1.860735752525624</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>17.75469602088433</v>
+        <v>2.885138103393704</v>
       </c>
       <c r="D8" t="n">
-        <v>17.99999122383633</v>
+        <v>2.924998573873403</v>
       </c>
       <c r="E8" t="n">
-        <v>11.6157786693359</v>
+        <v>1.887564033767084</v>
       </c>
       <c r="F8" t="n">
-        <v>11.45068155400384</v>
+        <v>1.860735752525624</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>27.67436332599606</v>
+        <v>4.49708404047436</v>
       </c>
       <c r="D9" t="n">
-        <v>28.23308687236272</v>
+        <v>4.587876616758941</v>
       </c>
       <c r="E9" t="n">
-        <v>11.6157786693359</v>
+        <v>1.887564033767084</v>
       </c>
       <c r="F9" t="n">
-        <v>11.45068155400384</v>
+        <v>1.860735752525624</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>22.83422057396207</v>
+        <v>3.710560843268837</v>
       </c>
       <c r="D10" t="n">
-        <v>23.46642648732075</v>
+        <v>3.813294304189621</v>
       </c>
       <c r="E10" t="n">
-        <v>11.6157786693359</v>
+        <v>1.887564033767084</v>
       </c>
       <c r="F10" t="n">
-        <v>11.45068155400384</v>
+        <v>1.860735752525624</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>27.31398617220806</v>
+        <v>4.438522752983809</v>
       </c>
       <c r="D11" t="n">
-        <v>26.48417432317772</v>
+        <v>4.303678327516379</v>
       </c>
       <c r="E11" t="n">
-        <v>11.6157786693359</v>
+        <v>1.887564033767084</v>
       </c>
       <c r="F11" t="n">
-        <v>11.45068155400384</v>
+        <v>1.860735752525624</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>13.45368487216873</v>
+        <v>2.186223791727419</v>
       </c>
       <c r="D12" t="n">
-        <v>12.76785241733676</v>
+        <v>2.074776017817223</v>
       </c>
       <c r="E12" t="n">
-        <v>11.6157786693359</v>
+        <v>1.887564033767084</v>
       </c>
       <c r="F12" t="n">
-        <v>11.45068155400384</v>
+        <v>1.860735752525624</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>38.15038858185761</v>
+        <v>6.199438144551862</v>
       </c>
       <c r="D13" t="n">
-        <v>38.82518488606978</v>
+        <v>6.30909254398634</v>
       </c>
       <c r="E13" t="n">
-        <v>11.6157786693359</v>
+        <v>1.887564033767084</v>
       </c>
       <c r="F13" t="n">
-        <v>11.45068155400384</v>
+        <v>1.860735752525624</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>62.09294717222875</v>
+        <v>10.09010391548717</v>
       </c>
       <c r="D14" t="n">
-        <v>62.62734092343061</v>
+        <v>10.17694290005747</v>
       </c>
       <c r="E14" t="n">
-        <v>11.6157786693359</v>
+        <v>1.887564033767084</v>
       </c>
       <c r="F14" t="n">
-        <v>11.45068155400384</v>
+        <v>1.860735752525624</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>30.11453496697649</v>
+        <v>4.893611932133679</v>
       </c>
       <c r="D15" t="n">
-        <v>30.90799058751784</v>
+        <v>5.022548470471649</v>
       </c>
       <c r="E15" t="n">
-        <v>11.6157786693359</v>
+        <v>1.887564033767084</v>
       </c>
       <c r="F15" t="n">
-        <v>11.45068155400384</v>
+        <v>1.860735752525624</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>36.767130976737</v>
+        <v>5.974658783719763</v>
       </c>
       <c r="D16" t="n">
-        <v>37.61116561416915</v>
+        <v>6.111814412302487</v>
       </c>
       <c r="E16" t="n">
-        <v>11.6157786693359</v>
+        <v>1.887564033767084</v>
       </c>
       <c r="F16" t="n">
-        <v>11.45068155400384</v>
+        <v>1.860735752525624</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>31.39831938088604</v>
+        <v>5.102226899393982</v>
       </c>
       <c r="D17" t="n">
-        <v>32.21786374443614</v>
+        <v>5.235402858470873</v>
       </c>
       <c r="E17" t="n">
-        <v>11.6157786693359</v>
+        <v>1.887564033767084</v>
       </c>
       <c r="F17" t="n">
-        <v>11.45068155400384</v>
+        <v>1.860735752525624</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
